--- a/excel/X_test.xlsx
+++ b/excel/X_test.xlsx
@@ -471,7 +471,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92.31471999999999</v>
+        <v>92.31502</v>
       </c>
       <c r="B2" t="n">
         <v>7.03</v>
@@ -501,7 +501,7 @@
         <v>0.00068</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008</v>
+        <v>0.0005</v>
       </c>
       <c r="L2" t="n">
         <v>0.128</v>
@@ -630,7 +630,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92.31362</v>
+        <v>92.31502</v>
       </c>
       <c r="B5" t="n">
         <v>7.03</v>
@@ -660,7 +660,7 @@
         <v>0.00068</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0019</v>
+        <v>0.0005</v>
       </c>
       <c r="L5" t="n">
         <v>0.128</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>92.31492</v>
+        <v>92.31502</v>
       </c>
       <c r="B16" t="n">
         <v>7.03</v>
@@ -1243,7 +1243,7 @@
         <v>0.00068</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="L16" t="n">
         <v>0.128</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>92.31422000000001</v>
+        <v>92.31502</v>
       </c>
       <c r="B23" t="n">
         <v>7.03</v>
@@ -1614,7 +1614,7 @@
         <v>0.00068</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0013</v>
+        <v>0.0005</v>
       </c>
       <c r="L23" t="n">
         <v>0.128</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>92.31382000000001</v>
+        <v>92.31502</v>
       </c>
       <c r="B32" t="n">
         <v>7.03</v>
@@ -2091,7 +2091,7 @@
         <v>0.00068</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0017</v>
+        <v>0.0005</v>
       </c>
       <c r="L32" t="n">
         <v>0.128</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>92.31482</v>
+        <v>92.31502</v>
       </c>
       <c r="B40" t="n">
         <v>7.03</v>
@@ -2515,7 +2515,7 @@
         <v>0.00068</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="L40" t="n">
         <v>0.128</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>92.31352</v>
+        <v>92.31502</v>
       </c>
       <c r="B49" t="n">
         <v>7.03</v>
@@ -2992,7 +2992,7 @@
         <v>0.00068</v>
       </c>
       <c r="K49" t="n">
-        <v>0.002</v>
+        <v>0.0005</v>
       </c>
       <c r="L49" t="n">
         <v>0.128</v>
